--- a/downloads/Resource_Request_List.xlsx
+++ b/downloads/Resource_Request_List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Resource Requests" sheetId="1" r:id="rId1"/>
+    <sheet name="Resources" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -424,77 +424,462 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:Q9"/>
   <cols>
-    <col min="1" max="1" width="50.83203125" customWidth="1"/>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="24.83203125" customWidth="1"/>
+    <col min="16" max="16" width="17.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
-        <v>Resource Requests Report</v>
+        <v>Resources Report</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <v>Name</v>
+        <v>Full Name</v>
       </c>
       <c r="B2" s="4" t="str">
-        <v>Email</v>
+        <v>Email ID</v>
       </c>
       <c r="C2" s="4" t="str">
-        <v>Mobile</v>
+        <v>Alternate Email ID</v>
       </c>
       <c r="D2" s="4" t="str">
-        <v>Requested By</v>
+        <v>Mobile Number</v>
       </c>
       <c r="E2" s="4" t="str">
-        <v>Requested Date</v>
+        <v>Role Name</v>
+      </c>
+      <c r="F2" s="4" t="str">
+        <v>Phone Number</v>
+      </c>
+      <c r="G2" s="4" t="str">
+        <v>Department Name</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <v>Client Name</v>
+      </c>
+      <c r="I2" s="4" t="str">
+        <v>Engagement Type</v>
+      </c>
+      <c r="J2" s="4" t="str">
+        <v>Pay Rate</v>
+      </c>
+      <c r="K2" s="4" t="str">
+        <v>Delete Reason</v>
+      </c>
+      <c r="L2" s="4" t="str">
+        <v>QBO Employee ID</v>
+      </c>
+      <c r="M2" s="4" t="str">
+        <v>Annual CTC</v>
+      </c>
+      <c r="N2" s="4" t="str">
+        <v>Manager Name</v>
+      </c>
+      <c r="O2" s="4" t="str">
+        <v>Reporting Manager Name</v>
+      </c>
+      <c r="P2" s="4" t="str">
+        <v>Employee Status</v>
+      </c>
+      <c r="Q2" s="4" t="str">
+        <v>Registered On</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="str">
-        <v>12333333333333333333333333333333333333333333333333 gdgfdgdfgfgggggggggggggggggggggggggggggggggggggggg</v>
+        <v>Rk  A</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>naresh@gmaillll.com</v>
+        <v>akkarajur@gmail.com</v>
       </c>
       <c r="C3" s="2" t="str">
-        <v>+91 234567890000001</v>
+        <v>-</v>
       </c>
       <c r="D3" s="2" t="str">
-        <v>Admin</v>
+        <v>+1 (389) 345-3543</v>
       </c>
       <c r="E3" s="2" t="str">
-        <v>08/24/2026</v>
+        <v>Employee</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <v>Time and Material</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="K3" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="L3" s="2">
+        <v>71</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="N3" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <v>2026-08-24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="str">
-        <v>Venkat Guttula</v>
+        <v>Lavanya  Kolla</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>venkatg@gmail.com</v>
+        <v>lavanya.kolla@pharmateksol.com</v>
       </c>
       <c r="C4" s="2" t="str">
-        <v>+1 (098) 765-4321</v>
+        <v>-</v>
       </c>
       <c r="D4" s="2" t="str">
+        <v>+1 (669) 666-4045</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <v>Vendor</v>
+      </c>
+      <c r="F4" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <v>Time and Material</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="K4" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="L4" s="2">
+        <v>67</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <v>Admin  Pharmatek</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="P4" s="2" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="Q4" s="2" t="str">
+        <v>2026-08-14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Rakesh  united</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>sowmya@pharmateksol.com</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <v>+1 (669) 666-4045</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>Time and Material</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="K5" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="L5" s="2">
+        <v>66</v>
+      </c>
+      <c r="M5" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <v>Admin  Pharmatek</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="P5" s="2" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="Q5" s="2" t="str">
+        <v>2026-08-14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Priyanka  Upputuri</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>priyaraocwa@gmail.com</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>+1 (897) 707-4065</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>Vendor</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="I6" s="2" t="str">
+        <v>Time and Material</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="K6" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="L6" s="2">
+        <v>63</v>
+      </c>
+      <c r="M6" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <v>Admin  Pharmatek</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="P6" s="2" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="Q6" s="2" t="str">
+        <v>2026-08-14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>UP  RAO</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>up.rao@pharmateksol.com</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>priyaraocwa@gmail.com</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <v>+91 9246226234</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <v>Time and Material</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="K7" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="L7" s="2">
+        <v>62</v>
+      </c>
+      <c r="M7" s="2">
+        <v>120000</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="P7" s="2" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="Q7" s="2" t="str">
+        <v>2026-08-14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>sushma  A</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>sushmaa@newmeksolutions.com</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>+1 (686) 865-7657657</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="I8" s="2" t="str">
+        <v>Time and Material</v>
+      </c>
+      <c r="J8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="K8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="L8" s="2">
+        <v>69</v>
+      </c>
+      <c r="M8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="N8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="O8" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="P8" s="2" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="Q8" s="2" t="str">
+        <v>2026-08-14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="str">
+        <v>Admin  Pharmatek</v>
+      </c>
+      <c r="B9" s="2" t="str">
+        <v>admin@pharmatek.com</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <v>+1 (999) 999-9999</v>
+      </c>
+      <c r="E9" s="2" t="str">
         <v>Admin</v>
       </c>
-      <c r="E4" s="2" t="str">
-        <v>08/20/2026</v>
+      <c r="F9" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="H9" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <v>Time and Material</v>
+      </c>
+      <c r="J9" s="2">
+        <v>50</v>
+      </c>
+      <c r="K9" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="L9" s="2">
+        <v>61</v>
+      </c>
+      <c r="M9" s="2">
+        <v>900000</v>
+      </c>
+      <c r="N9" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="O9" s="2" t="str">
+        <v>-</v>
+      </c>
+      <c r="P9" s="2" t="str">
+        <v>Submitted</v>
+      </c>
+      <c r="Q9" s="2" t="str">
+        <v>2026-01-13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q9"/>
   </ignoredErrors>
 </worksheet>
 </file>